--- a/Data/locT_UE.xlsx
+++ b/Data/locT_UE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/alanivory34428_ufl_edu/Documents/Desktop/School/Thesis/SSS_Occupancy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{AB969436-CE86-4396-9D61-A580E5F392BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B05BACC9-C150-4F6A-976E-3F7B88AD3D1E}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="8_{AB969436-CE86-4396-9D61-A580E5F392BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{201D3849-B969-4E59-87B4-703D260D580A}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{50502A11-8049-4347-9918-47058886ACB6}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{50502A11-8049-4347-9918-47058886ACB6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet3!$A$1:$N$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="701" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="162">
   <si>
     <t>OID</t>
   </si>
@@ -522,6 +522,12 @@
   </si>
   <si>
     <t>Imp_Range</t>
+  </si>
+  <si>
+    <t>Mount</t>
+  </si>
+  <si>
+    <t>Magnet</t>
   </si>
 </sst>
 </file>
@@ -868,7 +874,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82566BAF-EE76-4103-B0C9-33CC005E7C44}">
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
@@ -883,7 +889,7 @@
     <col min="17" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -932,8 +938,11 @@
       <c r="P1" s="9" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" s="9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="9">
         <v>13</v>
       </c>
@@ -974,7 +983,7 @@
         <v>0.88</v>
       </c>
       <c r="N2" s="9">
-        <f>CONVERT(D2,"in","cm")</f>
+        <f t="shared" ref="N2:N32" si="0">CONVERT(D2,"in","cm")</f>
         <v>45.72</v>
       </c>
       <c r="O2" s="9">
@@ -983,8 +992,11 @@
       <c r="P2" s="9">
         <v>69</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>17</v>
       </c>
@@ -1025,7 +1037,7 @@
         <v>0.4</v>
       </c>
       <c r="N3" s="9">
-        <f>CONVERT(D3,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>30.48</v>
       </c>
       <c r="O3" s="9">
@@ -1034,8 +1046,11 @@
       <c r="P3" s="9">
         <v>69</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>21</v>
       </c>
@@ -1076,7 +1091,7 @@
         <v>1.95</v>
       </c>
       <c r="N4" s="9">
-        <f>CONVERT(D4,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>60.96</v>
       </c>
       <c r="O4" s="9">
@@ -1085,8 +1100,11 @@
       <c r="P4" s="9">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>23</v>
       </c>
@@ -1127,7 +1145,7 @@
         <v>0.6</v>
       </c>
       <c r="N5" s="9">
-        <f>CONVERT(D5,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>38.1</v>
       </c>
       <c r="O5" s="9">
@@ -1136,8 +1154,11 @@
       <c r="P5" s="9">
         <v>75</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>24</v>
       </c>
@@ -1178,7 +1199,7 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="N6" s="9">
-        <f>CONVERT(D6,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>45.72</v>
       </c>
       <c r="O6" s="9">
@@ -1187,8 +1208,11 @@
       <c r="P6" s="9">
         <v>49</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>25</v>
       </c>
@@ -1229,7 +1253,7 @@
         <v>1.22</v>
       </c>
       <c r="N7" s="9">
-        <f>CONVERT(D7,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>38.1</v>
       </c>
       <c r="O7" s="9">
@@ -1238,8 +1262,11 @@
       <c r="P7" s="9">
         <v>74</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q7" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>48</v>
       </c>
@@ -1280,7 +1307,7 @@
         <v>1.3</v>
       </c>
       <c r="N8" s="9">
-        <f>CONVERT(D8,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>76.2</v>
       </c>
       <c r="O8" s="9">
@@ -1289,8 +1316,11 @@
       <c r="P8" s="9">
         <v>75</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>51</v>
       </c>
@@ -1331,7 +1361,7 @@
         <v>0.76</v>
       </c>
       <c r="N9" s="9">
-        <f>CONVERT(D9,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>76.2</v>
       </c>
       <c r="O9" s="9">
@@ -1340,8 +1370,11 @@
       <c r="P9" s="9">
         <v>66</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q9" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>52</v>
       </c>
@@ -1382,7 +1415,7 @@
         <v>1.4</v>
       </c>
       <c r="N10" s="9">
-        <f>CONVERT(D10,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>76.2</v>
       </c>
       <c r="O10" s="9">
@@ -1391,8 +1424,11 @@
       <c r="P10" s="9">
         <v>51</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>53</v>
       </c>
@@ -1433,7 +1469,7 @@
         <v>1.35</v>
       </c>
       <c r="N11" s="9">
-        <f>CONVERT(D11,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>106.67999999999999</v>
       </c>
       <c r="O11" s="9">
@@ -1442,8 +1478,11 @@
       <c r="P11" s="9">
         <v>58</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q11" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>54</v>
       </c>
@@ -1484,7 +1523,7 @@
         <v>1.36</v>
       </c>
       <c r="N12" s="9">
-        <f>CONVERT(D12,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>45.72</v>
       </c>
       <c r="O12" s="9">
@@ -1493,8 +1532,11 @@
       <c r="P12" s="9">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q12" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>57</v>
       </c>
@@ -1535,7 +1577,7 @@
         <v>0.88</v>
       </c>
       <c r="N13" s="9">
-        <f>CONVERT(D13,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>60.96</v>
       </c>
       <c r="O13" s="9">
@@ -1544,8 +1586,11 @@
       <c r="P13" s="9">
         <v>92</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q13" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>59</v>
       </c>
@@ -1586,7 +1631,7 @@
         <v>2.39</v>
       </c>
       <c r="N14" s="9">
-        <f>CONVERT(D14,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>76.2</v>
       </c>
       <c r="O14" s="9">
@@ -1595,8 +1640,11 @@
       <c r="P14" s="9">
         <v>67</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q14" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>60</v>
       </c>
@@ -1637,7 +1685,7 @@
         <v>1.8</v>
       </c>
       <c r="N15" s="9">
-        <f>CONVERT(D15,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>76.2</v>
       </c>
       <c r="O15" s="9">
@@ -1646,8 +1694,11 @@
       <c r="P15" s="9">
         <v>40</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q15" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>67</v>
       </c>
@@ -1688,7 +1739,7 @@
         <v>2.0699999999999998</v>
       </c>
       <c r="N16" s="9">
-        <f>CONVERT(D16,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>91.44</v>
       </c>
       <c r="O16" s="9">
@@ -1697,8 +1748,11 @@
       <c r="P16" s="9">
         <v>69</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q16" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>68</v>
       </c>
@@ -1739,7 +1793,7 @@
         <v>1.3</v>
       </c>
       <c r="N17" s="9">
-        <f>CONVERT(D17,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>60.96</v>
       </c>
       <c r="O17" s="9">
@@ -1748,8 +1802,11 @@
       <c r="P17" s="9">
         <v>89</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q17" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>71</v>
       </c>
@@ -1790,7 +1847,7 @@
         <v>0.93</v>
       </c>
       <c r="N18" s="9">
-        <f>CONVERT(D18,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>38.1</v>
       </c>
       <c r="O18" s="9">
@@ -1799,8 +1856,11 @@
       <c r="P18" s="9">
         <v>29</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q18" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>72</v>
       </c>
@@ -1841,7 +1901,7 @@
         <v>1.68</v>
       </c>
       <c r="N19" s="9">
-        <f>CONVERT(D19,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>60.96</v>
       </c>
       <c r="O19" s="9">
@@ -1850,8 +1910,11 @@
       <c r="P19" s="9">
         <v>67</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q19" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>75</v>
       </c>
@@ -1892,7 +1955,7 @@
         <v>1.81</v>
       </c>
       <c r="N20" s="9">
-        <f>CONVERT(D20,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>96.52</v>
       </c>
       <c r="O20" s="9">
@@ -1901,8 +1964,11 @@
       <c r="P20" s="9">
         <v>78</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q20" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>76</v>
       </c>
@@ -1943,7 +2009,7 @@
         <v>1.8</v>
       </c>
       <c r="N21" s="9">
-        <f>CONVERT(D21,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>38.1</v>
       </c>
       <c r="O21" s="9">
@@ -1952,8 +2018,11 @@
       <c r="P21" s="9">
         <v>76</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q21" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>84</v>
       </c>
@@ -1994,7 +2063,7 @@
         <v>0.8</v>
       </c>
       <c r="N22" s="9">
-        <f>CONVERT(D22,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>45.72</v>
       </c>
       <c r="O22" s="9">
@@ -2003,8 +2072,11 @@
       <c r="P22" s="9">
         <v>77</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q22" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>85</v>
       </c>
@@ -2045,7 +2117,7 @@
         <v>1.72</v>
       </c>
       <c r="N23" s="9">
-        <f>CONVERT(D23,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>172.72</v>
       </c>
       <c r="O23" s="9">
@@ -2054,8 +2126,11 @@
       <c r="P23" s="9">
         <v>64</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q23" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>86</v>
       </c>
@@ -2096,7 +2171,7 @@
         <v>3.4</v>
       </c>
       <c r="N24" s="9">
-        <f>CONVERT(D24,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>60.96</v>
       </c>
       <c r="O24" s="9">
@@ -2105,8 +2180,11 @@
       <c r="P24" s="9">
         <v>70</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q24" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>90</v>
       </c>
@@ -2147,7 +2225,7 @@
         <v>2</v>
       </c>
       <c r="N25" s="9">
-        <f>CONVERT(D25,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>76.2</v>
       </c>
       <c r="O25" s="9">
@@ -2156,8 +2234,11 @@
       <c r="P25" s="9">
         <v>43</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q25" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>91</v>
       </c>
@@ -2198,7 +2279,7 @@
         <v>2.6</v>
       </c>
       <c r="N26" s="9">
-        <f>CONVERT(D26,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>182.88</v>
       </c>
       <c r="O26" s="9">
@@ -2207,8 +2288,11 @@
       <c r="P26" s="9">
         <v>49</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q26" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>92</v>
       </c>
@@ -2249,7 +2333,7 @@
         <v>0.68</v>
       </c>
       <c r="N27" s="9">
-        <f>CONVERT(D27,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>38.1</v>
       </c>
       <c r="O27" s="9">
@@ -2258,8 +2342,11 @@
       <c r="P27" s="9">
         <v>31</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q27" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>94</v>
       </c>
@@ -2300,7 +2387,7 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="N28" s="9">
-        <f>CONVERT(D28,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>152.4</v>
       </c>
       <c r="O28" s="9">
@@ -2309,8 +2396,11 @@
       <c r="P28" s="9">
         <v>43</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q28" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>95</v>
       </c>
@@ -2351,7 +2441,7 @@
         <v>1.25</v>
       </c>
       <c r="N29" s="9">
-        <f>CONVERT(D29,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>60.96</v>
       </c>
       <c r="O29" s="9">
@@ -2360,8 +2450,11 @@
       <c r="P29" s="9">
         <v>69</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q29" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>170</v>
       </c>
@@ -2402,7 +2495,7 @@
         <v>0.5</v>
       </c>
       <c r="N30" s="9">
-        <f>CONVERT(D30,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>60.96</v>
       </c>
       <c r="O30" s="9">
@@ -2411,8 +2504,11 @@
       <c r="P30" s="9">
         <v>38</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q30" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>220</v>
       </c>
@@ -2453,7 +2549,7 @@
         <v>2.1</v>
       </c>
       <c r="N31" s="9">
-        <f>CONVERT(D31,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>60.96</v>
       </c>
       <c r="O31" s="9">
@@ -2462,8 +2558,11 @@
       <c r="P31" s="9">
         <v>42</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q31" s="9" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>300</v>
       </c>
@@ -2504,7 +2603,7 @@
         <v>2.4</v>
       </c>
       <c r="N32" s="9">
-        <f>CONVERT(D32,"in","cm")</f>
+        <f t="shared" si="0"/>
         <v>91.44</v>
       </c>
       <c r="O32" s="9">
@@ -2513,13 +2612,12 @@
       <c r="P32" s="9">
         <v>43</v>
       </c>
+      <c r="Q32" s="9" t="s">
+        <v>161</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P1" xr:uid="{82566BAF-EE76-4103-B0C9-33CC005E7C44}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P32">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:Q1" xr:uid="{82566BAF-EE76-4103-B0C9-33CC005E7C44}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
